--- a/Result/profitability/3551.xlsx
+++ b/Result/profitability/3551.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.21</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9425</v>
+        <v>2.09625</v>
       </c>
       <c r="N2" t="n">
-        <v>37.06375</v>
+        <v>37.3775</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.12</v>
       </c>
       <c r="M3" t="n">
-        <v>1.99375</v>
+        <v>2.15125</v>
       </c>
       <c r="N3" t="n">
-        <v>38.11625</v>
+        <v>38.44375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>2.04625</v>
+        <v>2.1475</v>
       </c>
       <c r="N4" t="n">
-        <v>39.48625</v>
+        <v>39.53749999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.11</v>
       </c>
       <c r="M5" t="n">
-        <v>1.91875</v>
+        <v>2.04625</v>
       </c>
       <c r="N5" t="n">
-        <v>39.09875</v>
+        <v>39.64</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>1.71125</v>
+        <v>1.82</v>
       </c>
       <c r="N6" t="n">
-        <v>39.80249999999999</v>
+        <v>40.54875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.13</v>
       </c>
       <c r="M7" t="n">
-        <v>1.59375</v>
+        <v>1.66625</v>
       </c>
       <c r="N7" t="n">
-        <v>41.3175</v>
+        <v>41.68</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2775</v>
+        <v>1.3375</v>
       </c>
       <c r="N8" t="n">
-        <v>41.5125</v>
+        <v>41.76375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.92</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>38.9425</v>
@@ -2029,7 +2029,7 @@
         <v>0.70875</v>
       </c>
       <c r="N13" t="n">
-        <v>37.01625</v>
+        <v>37.01625000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>861</v>
+      </c>
+      <c r="D75" t="n">
+        <v>522</v>
+      </c>
+      <c r="E75" t="n">
+        <v>340</v>
+      </c>
+      <c r="F75" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>196</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.80%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>27</v>
+      </c>
+      <c r="J75" t="n">
+        <v>223</v>
+      </c>
+      <c r="K75" t="n">
+        <v>182</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.15875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.85625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1951219512195121</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.010000000000005</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05368589743589758</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.330000000000005</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1232915717539864</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
